--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -1,30 +1,151 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView tabRatio="600"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200"/>
   </bookViews>
   <sheets>
     <sheet name="Upgrade_Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr/>
+  <extLst>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CriticalChance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CriticalDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sword</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력&lt;sprite name="sword"&gt; 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 감소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경험치 획득량  증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">치명타 확률 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">치명타 피해량 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1}) % 만큼 증가합니다.\n {2}/{3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1}) % 만큼 감소합니다.\n {2}/{3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1}) % 만큼 증가합니다.\n {2}/{3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1}) % 만큼 증가합니다.\n {2}/{3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1}) % 만큼 증가합니다.\n {2}/{3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 치명타 확률이 {0}({1}) % 만큼 증가합니다.\n {2}/{3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 치명타 피해량이 {0}({1}) % 만큼 증가합니다.\n {2}/{3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -32,11 +153,20 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -51,21 +181,11 @@
       <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
-      <left>
-        <color indexed="64"/>
-      </left>
-      <right>
-        <color indexed="64"/>
-      </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -73,82 +193,23 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -438,14 +499,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
   </sheetPr>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
-    <col min="3" max="3" width="48.5703125" customWidth="1"/>
+    <col min="2" max="2" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.92578125" customWidth="1"/>
     <col min="5" max="5" width="15.140625" customWidth="1"/>
     <col min="6" max="6" width="18.78515625" customWidth="1"/>
@@ -454,83 +514,47 @@
     <col min="10" max="10" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <v>upgrade_name</v>
-        <is>
-          <t xml:space="preserve">upgrade_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <v>need_money</v>
-        <is>
-          <t xml:space="preserve">need_money</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <v>upgrade_value</v>
-        <is>
-          <t xml:space="preserve">upgrade_value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <v>max_upgrade_count</v>
-        <is>
-          <t xml:space="preserve">max_upgrade_count</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <v>upgrade_type</v>
-        <is>
-          <t xml:space="preserve">upgrade_type</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <v>stat_type</v>
-        <is>
-          <t xml:space="preserve">stat_type</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <v>growth_rate</v>
-        <is>
-          <t xml:space="preserve">growth_rate</t>
-        </is>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>110001</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-        </is>
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D2" s="1">
         <v>60</v>
@@ -541,37 +565,28 @@
       <c r="F2" s="1">
         <v>100</v>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackDamage</t>
-        </is>
+      <c r="G2" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="J2" s="1">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>110002</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-        </is>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D3" s="1">
         <v>85</v>
@@ -582,37 +597,25 @@
       <c r="F3" s="1">
         <v>50</v>
       </c>
-      <c r="H3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackInterval</t>
-        </is>
+      <c r="H3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="J3" s="1">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
         <v>110003</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-        </is>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D4" s="1">
         <v>120</v>
@@ -623,37 +626,25 @@
       <c r="F4" s="1">
         <v>100</v>
       </c>
-      <c r="H4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MaxHp</t>
-        </is>
+      <c r="H4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="J4" s="1">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A5" s="1">
         <v>110004</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-        </is>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D5" s="1">
         <v>140</v>
@@ -664,31 +655,25 @@
       <c r="F5" s="1">
         <v>100</v>
       </c>
-      <c r="H5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NonTrainUpgrade</t>
-        </is>
+      <c r="G5" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="J5" s="1">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A6" s="1">
         <v>110005</v>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-        </is>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D6" s="1">
         <v>140</v>
@@ -699,31 +684,22 @@
       <c r="F6" s="1">
         <v>100</v>
       </c>
-      <c r="H6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NonTrainUpgrade</t>
-        </is>
+      <c r="H6" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="J6" s="1">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A7" s="1">
         <v>110006</v>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">치명타 확률 {0}/{1} % 증가</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포탑들의 치명타 확률이 {0}({1})만큼 증가합니다.</t>
-        </is>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
@@ -734,37 +710,25 @@
       <c r="F7" s="1">
         <v>30</v>
       </c>
-      <c r="H7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CriticalChance</t>
-        </is>
+      <c r="H7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="J7" s="1">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A8" s="1">
         <v>110007</v>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">치명타 피해량 {0}/{1} % 증가</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포탑들의 치명타 피해량이 {0}({1})만큼 증가합니다.</t>
-        </is>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D8" s="1">
         <v>120</v>
@@ -775,23 +739,19 @@
       <c r="F8" s="1">
         <v>50</v>
       </c>
-      <c r="H8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CriticalDamage</t>
-        </is>
+      <c r="H8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="J8" s="1">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="33">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="33">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="33">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="33">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="33">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="33">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="33">
   <si>
     <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -1,120 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
-  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Upgrade_Data" sheetId="1" r:id="rId4"/>
+    <sheet name="Upgrade_Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="33">
-  <si>
-    <t xml:space="preserve">골드 &lt;sprite name="Coin"&gt;획득량 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CriticalDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CriticalChance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1}) 만큼 증가합니다.\n {2}/{3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 치명타 피해량이 {0}({1}) 만큼 증가합니다.\n {2}/{3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1}) 만큼 감소합니다.\n {2}/{3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 치명타 확률이 {0}({1}) 만큼 증가합니다.\n {2}/{3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">치명타 피해량 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">치명타 확률 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">경험치 획득량  증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">growth_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력&lt;sprite name="sword"&gt; 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1}) 만큼 증가합니다.\n {2}/{3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1}) 만큼 증가합니다.\n {2}/{3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1}) 만큼 증가합니다.\n {2}/{3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coin</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -154,7 +53,7 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -177,18 +76,16 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -253,6 +150,74 @@
       <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -539,9 +504,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="47.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="60.140625" style="1" bestFit="1" customWidth="1"/>
@@ -553,47 +521,83 @@
     <col min="10" max="10" width="12.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <v>upgrade_name</v>
+        <is>
+          <t xml:space="preserve">upgrade_name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <v>need_money</v>
+        <is>
+          <t xml:space="preserve">need_money</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <v>upgrade_value</v>
+        <is>
+          <t xml:space="preserve">upgrade_value</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <v>max_upgrade_count</v>
+        <is>
+          <t xml:space="preserve">max_upgrade_count</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <v>icon_id</v>
+        <is>
+          <t xml:space="preserve">icon_id</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <v>upgrade_type</v>
+        <is>
+          <t xml:space="preserve">upgrade_type</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <v>stat_type</v>
+        <is>
+          <t xml:space="preserve">stat_type</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <v>growth_rate</v>
+        <is>
+          <t xml:space="preserve">growth_rate</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2">
       <c r="A2" s="2">
         <v>110001</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
+      <c r="B2" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110001_Name</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110001_Desc</t>
+        </is>
       </c>
       <c r="D2" s="2">
         <v>60</v>
@@ -604,28 +608,43 @@
       <c r="F2" s="2">
         <v>100</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>1</v>
+      <c r="G2" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">sword</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackDamage</t>
+        </is>
       </c>
       <c r="J2" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.065</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3">
       <c r="A3" s="2">
         <v>110002</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
+      <c r="B3" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110002_Name</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110002_Desc</t>
+        </is>
       </c>
       <c r="D3" s="2">
         <v>85</v>
@@ -636,25 +655,37 @@
       <c r="F3" s="2">
         <v>50</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
+      <c r="H3" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackInterval</t>
+        </is>
       </c>
       <c r="J3" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.065</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4">
       <c r="A4" s="2">
         <v>110003</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>27</v>
+      <c r="B4" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110003_Name</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110003_Desc</t>
+        </is>
       </c>
       <c r="D4" s="2">
         <v>120</v>
@@ -665,25 +696,37 @@
       <c r="F4" s="2">
         <v>100</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>30</v>
+      <c r="H4" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">MaxHp</t>
+        </is>
       </c>
       <c r="J4" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.065</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5">
       <c r="A5" s="2">
         <v>110004</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>25</v>
+      <c r="B5" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110004_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110004_Desc</t>
+        </is>
       </c>
       <c r="D5" s="2">
         <v>140</v>
@@ -694,25 +737,37 @@
       <c r="F5" s="2">
         <v>100</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>8</v>
+      <c r="G5" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Coin</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">NonTrainUpgrade</t>
+        </is>
       </c>
       <c r="J5" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.065</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6">
       <c r="A6" s="2">
         <v>110005</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
+      <c r="B6" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110005_Name</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110005_Desc</t>
+        </is>
       </c>
       <c r="D6" s="2">
         <v>140</v>
@@ -723,22 +778,31 @@
       <c r="F6" s="2">
         <v>100</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>8</v>
+      <c r="H6" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">NonTrainUpgrade</t>
+        </is>
       </c>
       <c r="J6" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.065</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7">
       <c r="A7" s="2">
         <v>110006</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
+      <c r="B7" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110006_Name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110006_Desc</t>
+        </is>
       </c>
       <c r="D7" s="2">
         <v>100</v>
@@ -749,25 +813,37 @@
       <c r="F7" s="2">
         <v>30</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>9</v>
+      <c r="H7" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">CriticalChance</t>
+        </is>
       </c>
       <c r="J7" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.065</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8">
       <c r="A8" s="2">
         <v>110007</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
+      <c r="B8" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110007_Name</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Upgrade_110007_Desc</t>
+        </is>
       </c>
       <c r="D8" s="2">
         <v>120</v>
@@ -778,14 +854,20 @@
       <c r="F8" s="2">
         <v>50</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>6</v>
+      <c r="H8" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">CriticalDamage</t>
+        </is>
       </c>
       <c r="J8" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.065</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -1,25 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600"/>
+    <workbookView windowWidth="28545" windowHeight="11700"/>
   </bookViews>
   <sheets>
-    <sheet name="Upgrade_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Upgrade_Data" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CriticalChance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CriticalDamage</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -50,17 +151,22 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left>
         <color indexed="64"/>
       </left>
@@ -73,10 +179,64 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+  <cellStyleXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -84,16 +244,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf/>
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -126,98 +287,103 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE5"/>
+          <bgColor rgb="FFB8CCE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE5"/>
+          <bgColor rgb="FFB8CCE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
-      <tableStyleElement type="wholeTable" size="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="8">
+      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="secondColumnStripe" size="1"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="5"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="10"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="9"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="8"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -504,12 +670,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet1">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="47.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="60.140625" style="1" bestFit="1" customWidth="1"/>
@@ -521,83 +684,47 @@
     <col min="10" max="10" width="12.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <v>upgrade_name</v>
-        <is>
-          <t xml:space="preserve">upgrade_name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <v>need_money</v>
-        <is>
-          <t xml:space="preserve">need_money</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <v>upgrade_value</v>
-        <is>
-          <t xml:space="preserve">upgrade_value</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <v>max_upgrade_count</v>
-        <is>
-          <t xml:space="preserve">max_upgrade_count</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <v>upgrade_type</v>
-        <is>
-          <t xml:space="preserve">upgrade_type</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <v>stat_type</v>
-        <is>
-          <t xml:space="preserve">stat_type</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <v>growth_rate</v>
-        <is>
-          <t xml:space="preserve">growth_rate</t>
-        </is>
+    <row r="1" spans="1:10">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10">
       <c r="A2" s="2">
         <v>110001</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110001_Name</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110001_Desc</t>
-        </is>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D2" s="2">
         <v>60</v>
@@ -608,43 +735,28 @@
       <c r="F2" s="2">
         <v>100</v>
       </c>
-      <c r="G2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">sword</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackDamage</t>
-        </is>
+      <c r="G2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="J2" s="2">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10">
       <c r="A3" s="2">
         <v>110002</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110002_Name</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110002_Desc</t>
-        </is>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D3" s="2">
         <v>85</v>
@@ -655,37 +767,25 @@
       <c r="F3" s="2">
         <v>50</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackInterval</t>
-        </is>
+      <c r="H3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="J3" s="2">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10">
       <c r="A4" s="2">
         <v>110003</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110003_Name</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110003_Desc</t>
-        </is>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D4" s="2">
         <v>120</v>
@@ -696,37 +796,25 @@
       <c r="F4" s="2">
         <v>100</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MaxHp</t>
-        </is>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="J4" s="2">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10">
       <c r="A5" s="2">
         <v>110004</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110004_Name</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110004_Desc</t>
-        </is>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D5" s="2">
         <v>140</v>
@@ -737,37 +825,25 @@
       <c r="F5" s="2">
         <v>100</v>
       </c>
-      <c r="G5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Coin</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NonTrainUpgrade</t>
-        </is>
+      <c r="G5" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J5" s="2">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10">
       <c r="A6" s="2">
         <v>110005</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110005_Name</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110005_Desc</t>
-        </is>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D6" s="2">
         <v>140</v>
@@ -778,31 +854,22 @@
       <c r="F6" s="2">
         <v>100</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NonTrainUpgrade</t>
-        </is>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J6" s="2">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10">
       <c r="A7" s="2">
         <v>110006</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110006_Name</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110006_Desc</t>
-        </is>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D7" s="2">
         <v>100</v>
@@ -811,63 +878,45 @@
         <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CriticalChance</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="J7" s="2">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10">
       <c r="A8" s="2">
         <v>110007</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110007_Name</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Upgrade_110007_Desc</t>
-        </is>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="2">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>50</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CriticalDamage</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="J8" s="2">
-        <v>1.065</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -9,110 +9,109 @@
   <sheets>
     <sheet name="Upgrade_Data" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CriticalChance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CriticalDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth_rate</t>
+  </si>
   <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
+    <t xml:space="preserve">Coin</t>
+  </si>
+  <si>
     <t xml:space="preserve">icon_id</t>
   </si>
   <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">growth_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coin</t>
+    <t xml:space="preserve">sword</t>
   </si>
   <si>
     <t xml:space="preserve">MaxHp</t>
   </si>
   <si>
-    <t xml:space="preserve">sword</t>
+    <t xml:space="preserve">Upgrade_110003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110001_Desc</t>
   </si>
   <si>
     <t xml:space="preserve">Upgrade_110003_Desc</t>
   </si>
   <si>
+    <t xml:space="preserve">Upgrade_110002_Desc</t>
+  </si>
+  <si>
     <t xml:space="preserve">max_upgrade_count</t>
   </si>
   <si>
-    <t xml:space="preserve">Upgrade_110001_Desc</t>
+    <t xml:space="preserve">Upgrade_110007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade_110007_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Upgrade_110002_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Upgrade_110003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110007_Desc</t>
-  </si>
-  <si>
     <t xml:space="preserve">Upgrade_110006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CriticalChance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CriticalDamage</t>
   </si>
 </sst>
 </file>
@@ -254,15 +253,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -361,27 +352,98 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE5"/>
+          <bgColor rgb="FFB8CCE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE5"/>
+          <bgColor rgb="FFB8CCE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="8">
-      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="secondColumnStripe" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="6">
+      <tableStyleElement type="headerRow" size="1" dxfId="3"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="2"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="1"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="5"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="10"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="9"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="8"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="7"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
+      <tableStyleElement type="wholeTable" size="1" dxfId="4"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="9"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="8"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="7"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="5"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="6"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -686,34 +748,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -721,28 +783,28 @@
         <v>110001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2">
         <v>60</v>
       </c>
       <c r="E2" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2">
         <v>1.0649999999999999</v>
@@ -753,25 +815,25 @@
         <v>110002</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2">
         <v>85</v>
       </c>
       <c r="E3" s="2">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="F3" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J3" s="2">
         <v>1.0649999999999999</v>
@@ -782,25 +844,25 @@
         <v>110003</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2">
         <v>120</v>
       </c>
       <c r="E4" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J4" s="2">
         <v>1.0649999999999999</v>
@@ -811,25 +873,25 @@
         <v>110004</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2">
         <v>140</v>
       </c>
       <c r="E5" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2">
         <v>1.0649999999999999</v>
@@ -840,22 +902,22 @@
         <v>110005</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2">
         <v>140</v>
       </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2">
         <v>1.0649999999999999</v>
@@ -866,25 +928,25 @@
         <v>110006</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2">
         <v>100</v>
       </c>
       <c r="E7" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="J7" s="2">
         <v>1.0649999999999999</v>
@@ -895,25 +957,25 @@
         <v>110007</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2">
         <v>60</v>
       </c>
       <c r="E8" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J8" s="2">
         <v>1.0649999999999999</v>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t xml:space="preserve">need_money</t>
   </si>
@@ -789,13 +789,13 @@
         <v>21</v>
       </c>
       <c r="D2" s="2">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E2" s="2">
         <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>16</v>
@@ -807,7 +807,7 @@
         <v>3</v>
       </c>
       <c r="J2" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -821,7 +821,7 @@
         <v>23</v>
       </c>
       <c r="D3" s="2">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="E3" s="2">
         <v>-5</v>
@@ -836,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="J3" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="D4" s="2">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2">
         <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>4</v>
@@ -865,7 +865,7 @@
         <v>17</v>
       </c>
       <c r="J4" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -879,7 +879,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="2">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E5" s="2">
         <v>5</v>
@@ -894,7 +894,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -908,7 +908,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="2">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
@@ -920,7 +920,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -934,7 +934,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
@@ -949,7 +949,7 @@
         <v>7</v>
       </c>
       <c r="J7" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.065</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -963,13 +963,13 @@
         <v>25</v>
       </c>
       <c r="D8" s="2">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>4</v>
@@ -978,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="J8" s="2">
-        <v>1.0649999999999999</v>
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -934,7 +934,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
@@ -949,7 +949,7 @@
         <v>7</v>
       </c>
       <c r="J7" s="2">
-        <v>1.065</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -963,7 +963,7 @@
         <v>25</v>
       </c>
       <c r="D8" s="2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
@@ -978,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="J8" s="2">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="33">
   <si>
     <t xml:space="preserve">need_money</t>
   </si>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -1,164 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
-  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28545" windowHeight="11700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Upgrade_Data" sheetId="1" r:id="rId4"/>
+    <sheet name="Upgrade_Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="33">
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CriticalChance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CriticalDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">growth_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade_110006_Name</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="7">
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -183,75 +79,22 @@
       </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
@@ -446,6 +289,74 @@
       <tableStyleElement type="firstColumnStripe" size="1" dxfId="6"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -731,258 +642,283 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
-    <col min="2" max="2" width="47.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.92578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.78515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.78515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.35546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" style="1" customWidth="1"/>
+    <col width="47.140625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="60.140625" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="12.92578125" customWidth="1" style="1" min="4" max="4"/>
+    <col width="15.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="18.78515625" customWidth="1" style="1" min="6" max="6"/>
+    <col width="12.78515625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="19.35546875" customWidth="1" style="1" min="8" max="8"/>
+    <col width="12.140625" customWidth="1" style="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>12</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>upgrade_name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>need_money</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>upgrade_value</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_upgrade_count</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>icon_id</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>upgrade_type</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>stat_type</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>growth_rate</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2">
+    <row r="2">
+      <c r="A2" s="2" t="n">
         <v>110001</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110001_Name</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110001_Desc</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="G2" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade/Upgrade_110001</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>AttackDamage</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>1.15</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2">
+    <row r="3">
+      <c r="A3" s="2" t="n">
         <v>110002</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110002_Name</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110002_Desc</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="2" t="n">
         <v>-5</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Upgrade/Upgrade_110002</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>AttackInterval</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>110003</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110003_Name</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110003_Desc</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="2">
+      <c r="F4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Upgrade/Upgrade_110003</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>110004</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110004_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110004_Desc</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade/Upgrade_110004</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>NonTrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>110006</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110006_Name</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110006_Desc</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Upgrade/Upgrade_110006</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>CriticalChance</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>1.15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2">
-        <v>110003</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2">
-        <v>90</v>
-      </c>
-      <c r="E4" s="2">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2">
-        <v>100</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2">
-        <v>110004</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="2">
-        <v>120</v>
-      </c>
-      <c r="E5" s="2">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2">
-        <v>20</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2">
-        <v>110005</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2">
-        <v>90</v>
-      </c>
-      <c r="E6" s="2">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2">
-        <v>110006</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2">
-        <v>120</v>
-      </c>
-      <c r="E7" s="2">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2">
-        <v>110007</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2">
-        <v>130</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col width="47.140625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -777,7 +777,7 @@
       <c r="F3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Upgrade/Upgrade_110002</t>
         </is>
@@ -819,7 +819,7 @@
       <c r="F4" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Upgrade/Upgrade_110003</t>
         </is>
@@ -839,54 +839,54 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>110004</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Upgrade_110004_Name</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Upgrade_110004_Desc</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>120</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" t="n">
         <v>20</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Upgrade/Upgrade_110004</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>NonTrainUpgrade</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" t="n">
         <v>1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>110006</v>
+        <v>110008</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Upgrade_110006_Name</t>
+          <t>Upgrade_110008_Name</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Upgrade_110006_Desc</t>
+          <t>Upgrade_110008_Desc</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -898,23 +898,92 @@
       <c r="F6" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Upgrade/Upgrade_110006</t>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade/Upgrade_110008</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>TrainUpgrade</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>CriticalChance</t>
+          <t>NonTrainUpgrade</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>110009</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110009_Name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110009_Desc</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade/Upgrade_110009</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>NonTrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>110010</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110010_Name</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110010_Desc</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade/Upgrade_110010</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>NonTrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -893,7 +893,7 @@
         <v>120</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>20</v>

--- a/Assets/02_Resources/Data/UpgradeData.xlsx
+++ b/Assets/02_Resources/Data/UpgradeData.xlsx
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col width="47.140625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -711,6 +711,21 @@
           <t>growth_rate</t>
         </is>
       </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>stats</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -753,6 +768,14 @@
       <c r="J2" s="2" t="n">
         <v>1.15</v>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>LevelUp</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -795,6 +818,14 @@
       <c r="J3" s="2" t="n">
         <v>1.15</v>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>LevelUp</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -837,42 +868,58 @@
       <c r="J4" s="2" t="n">
         <v>1.11</v>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>LevelUp</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="2" t="n">
         <v>110004</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Upgrade_110004_Name</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Upgrade_110004_Desc</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Upgrade/Upgrade_110004</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NonTrainUpgrade</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>GoldGain</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>1.13</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>LevelUp</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -911,6 +958,14 @@
       <c r="J6" s="2" t="n">
         <v>1.13</v>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>LevelUp</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -948,6 +1003,14 @@
       <c r="J7" s="2" t="n">
         <v>1.13</v>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>LevelUp</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -984,6 +1047,409 @@
       </c>
       <c r="J8" s="2" t="n">
         <v>1.13</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>LevelUp</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>110011</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110011_Name</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110011_Desc</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem/Item_110011</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>AttackDamage:4</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>110012</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110012_Name</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110012_Desc</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem/Item_110012</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>AttackDamage:15;AttackRange:-8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>110013</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110013_Name</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110013_Desc</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem/Item_110013</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>AttackRange:8</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>110014</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110014_Name</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110014_Desc</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem/Item_110014</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>AttackInterval:-10;MaxHp:-5</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>110015</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110015_Name</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110015_Desc</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem/Item_110015</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>AttackInterval:-6</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>110016</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110016_Name</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110016_Desc</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem/Item_110016</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>AttackArea:5</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>110017</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110017_Name</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110017_Desc</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem/Item_110017</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>GoldGain</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>110018</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110018_Name</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade_110018_Desc</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem/Item_110018</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>TrainUpgrade</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>ShopItem</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>MaxHp:5</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
